--- a/business_surveys/045_engagement_drivers_exploration_survey--business_surveys.xlsx
+++ b/business_surveys/045_engagement_drivers_exploration_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1141,17 +1141,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>employee_engagement_drivers_choices</t>
+          <t>manager_engagement_drivers_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_autonomy</t>
+          <t>job_security</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Job Autonomy</t>
+          <t>Job Security</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>job_security</t>
+          <t>clear_communication</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Job Security</t>
+          <t>Clear Communication</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>clear_communication</t>
+          <t>recognition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Clear Communication</t>
+          <t>Recognition</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>recognition</t>
+          <t>clear_expectations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Recognition</t>
+          <t>Clear Expectations</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>clear_expectations</t>
+          <t>job_autonomy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Clear Expectations</t>
+          <t>Job Autonomy</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>job_autonomy</t>
+          <t>clear_feedback</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Job Autonomy</t>
+          <t>Clear Feedback</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>clear_feedback</t>
+          <t>learning_opportunities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Clear Feedback</t>
+          <t>Learning Opportunities</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>learning_opportunities</t>
+          <t>manager_development</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Learning Opportunities</t>
+          <t>Manager Development</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>manager_development</t>
+          <t>positive_workplace_environment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manager Development</t>
+          <t>Positive Workplace Environment</t>
         </is>
       </c>
     </row>
@@ -1299,29 +1299,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>positive_workplace_environment</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Positive Workplace Environment</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>manager_engagement_drivers_choices</t>
+          <t>employee_job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>collaboration</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1384,29 +1384,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>employee_job_satisfaction_choices</t>
+          <t>manager_job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1469,29 +1469,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Somewhat Dissatisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>manager_job_satisfaction_choices</t>
+          <t>manager_job_security_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>highly_secure</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Very Dissatisfied</t>
+          <t>Highly Secure</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>highly_secure</t>
+          <t>moderately_secure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Highly Secure</t>
+          <t>Moderately Secure</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>moderately_secure</t>
+          <t>somewhat_secure</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Moderately Secure</t>
+          <t>Somewhat Secure</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>somewhat_secure</t>
+          <t>not_very_secure</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Somewhat Secure</t>
+          <t>Not Very Secure</t>
         </is>
       </c>
     </row>
@@ -1554,27 +1554,10 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>not_very_secure</t>
+          <t>not_at_all_secure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Not Very Secure</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>manager_job_security_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>not_at_all_secure</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>Not at All Secure</t>
         </is>
